--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source de vérité — 1 ligne par version de fiche · N° fiche = FT-&lt;référence&gt; (figé) · Mise à jour : 22/06/2026</t>
+          <t>Source de vérité — 1 ligne par version de fiche · N° fiche = FT-&lt;référence&gt; (figé) · Mise à jour : 12/10/2026</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Multidièdre charbon actif</t>
+          <t>Filtre polydièdre à poches rigides, charbon actif</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1512,22 +1512,22 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Moléculaire (ISO 10121)</t>
+          <t>Moléculaire (aucune classe ISO 10121 affichée)</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.1</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Créée — charbon actif poches rigides/dièdre, mono-classe 292 mm</t>
+          <t>Contenu retravaillé v1.1 (12/10) — à valider PA : sous-titre, descriptif et points clés rédigés par PA, photo Netair, courbe 2023 (0-4 000 m³/h, 122 Pa), codes CA</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>Charbon pur (gaz), pas de classe ePM. Courbe 2020 QL-CARB (8,073·v²+13,383·v+2,929 ; ΔP@3400≈98). Piège 2023 F7=F8=base écarté. Parois POLYESTER, feu NA, T° 40°C (efficacité), HR 70%. Combinable F7/F9 option. Capacité adsorption n.c.→R&amp;D. Photo CARB_BLEND placeholder.</t>
+          <t>v1.1 12/10/2026, décisions PA : sous-titre « Filtre polydièdre à charbon actif » ; descriptif et points clés rédigés par PA (grains de charbon actif entre deux non-tissés, version combinée avec voile filtrant, s'utilise en complément d'un filtre à particules) ; aucune mention ISO 10121 tant qu'aucun essai ; capacité d'adsorption sans chiffre (veille concurrents : aucun % massique publié) ; parois « Plastique » (convention AZUR, source polyester) ; feu « Non classé » ; T° 40 °C max. (efficacité) ; photo Netair « Azur Carb.png ». Courbe 2023 (fiche SV-GD CARB 2023, charbon seul, 7 pts mesurés 1 000→4 000 m³/h ; 8,035·v²+24,392·v−2,500), ΔP@3400 = 122 Pa (v1.0 : courbe 2020, 98 Pa). Débits 490×592 = 2 810, 287×592 = 1 650. Codes NETCARB-AZUR-CA-LxHxP (clé ref_classe), combinée NETCARB-AZUR-F7CA-… Note sous tableau réduite à 1 ligne (fiche sortait sur 3 pages).</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1527,7 +1527,7 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Contenu retravaillé v1.1 (12/10) — à valider PA : sous-titre, descriptif et points clés rédigés par PA, photo Netair, courbe 2023 (0-4 000 m³/h, 122 Pa), codes CA</t>
+          <t>Validée PA — contenu retravaillé 12/10 (sous-titre, descriptif et points clés PA, courbe 2023 à 122 Pa, photo Netair, codes CA)</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1517,7 +1517,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>v1.1</t>
+          <t>v1.2</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Validée PA — contenu retravaillé 12/10 (sous-titre, descriptif et points clés PA, courbe 2023 à 122 Pa, photo Netair, codes CA)</t>
+          <t>Validée PA — contenu retravaillé 12/10 (sous-titre, descriptif et points clés PA, courbe 2023 à 122 Pa, photo Netair, codes CA) ; v1.2 12/10 : ligne Fonction et badge : « gaz, odeurs et COV » au lieu des 4 gaz non mesurés (accord PA)</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Polydièdre charbon actif</t>
+          <t>Filtre caisson multidièdre, charbon actif</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1574,22 +1574,22 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Moléculaire (ISO 10121)</t>
+          <t>Moléculaire (aucune classe ISO 10121 affichée)</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.1</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Créée — charbon actif polydièdre, mono-classe 292 mm (courbe partagée AZUR)</t>
+          <t>Validée PA — contenu retravaillé 12/10 (sous-titre, descriptif et points clés PA, photo Netair cadre noir, sans courbe : fiche 1 page, polluants « gaz, odeurs et COV », codes CA)</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>Polydièdre charbon (gaz). ⚠ Aucune courbe ΔP V-CARB mesurée → courbe pack charbon 292 mm de SV-GD/QL partagée (à mesurer R&amp;D). Nominal 3000, ΔP@3000≈80. Combinable F7. T° 40°C, HR 70%, feu NA. Parois polyester à confirmer. Photo Q-carb (code visible→remplacer). Classe LD/MD/HD &amp; capacité→R&amp;D.</t>
+          <t>v1.1 12/10/2026, décisions PA : base NETCARB AZUR v1.1. Sous-titre « Filtre caisson multidièdre à charbon actif » ; descriptif et points clés PA ; même média qu'AZUR (grains entre deux médias non tissés) ; capacité sans chiffre ; parois « Plastique » ; aucune mention ISO 10121 ; polluants « gaz, odeurs et COV » (badge + Fonction) au lieu des 4 gaz non mesurés. PAS DE COURBE pour le moment (clé sans_courbe) : aucune mesure du V-CARB charbon seul ; la fiche V-CARB F7 2018 (combinée) recopie QL-CARB F9 2013, l'ancienne courbe empruntée (QL-CARB 2013) est abandonnée. Débits 3 000 / 2 480 / 1 450. Codes NETCARB-NIVAL-CA-LxHxP. Donnée non affichée : masse de charbon 2 748 g (V-CARB F7 2018).</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1604,7 +1604,7 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>v1.1 12/10/2026, décisions PA : base NETCARB AZUR v1.1. Sous-titre « Filtre caisson multidièdre à charbon actif » ; descriptif et points clés PA ; même média qu'AZUR (grains entre deux médias non tissés) ; capacité sans chiffre ; parois « Plastique » ; aucune mention ISO 10121 ; polluants « gaz, odeurs et COV » (badge + Fonction) au lieu des 4 gaz non mesurés. PAS DE COURBE pour le moment (clé sans_courbe) : aucune mesure du V-CARB charbon seul ; la fiche V-CARB F7 2018 (combinée) recopie QL-CARB F9 2013, l'ancienne courbe empruntée (QL-CARB 2013) est abandonnée. Débits 3 000 / 2 480 / 1 450. Codes NETCARB-NIVAL-CA-LxHxP. Donnée non affichée : masse de charbon 2 748 g (V-CARB F7 2018).</t>
+          <t>v1.1 12/10/2026, décisions PA : base NETCARB AZUR v1.1. Sous-titre « Filtre caisson multidièdre à charbon actif » ; descriptif et points clés PA ; même média qu'AZUR (grains entre deux médias non tissés) ; capacité sans chiffre ; parois « Plastique » ; aucune mention ISO 10121 ; polluants « gaz, odeurs et COV » (badge + Fonction) au lieu des 4 gaz non mesurés. PAS DE COURBE pour le moment (clé sans_courbe) : aucune mesure du V-CARB charbon seul ; la fiche V-CARB F7 2018 (combinée) recopie QL-CARB F9 2013, l'ancienne courbe empruntée (QL-CARB 2013) est abandonnée. Formats corrigés le 12/10 (v1.1 non diffusée) : 610×610 (3 190), 305×610 (1 590), 592×592 (3 000), 287×592 (1 450), comme NETCEL V NIVAL. Codes NETCARB-NIVAL-CA-LxHxP. Donnée non affichée : masse de charbon 2 748 g (V-CARB F7 2018).</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1626,32 +1626,32 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Poches charbon actif</t>
+          <t>Filtre à poches souples, particules + charbon actif</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>F9</t>
+          <t>F7</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>ePM1 80% + CA (ISO 10121)</t>
+          <t>ePM1 50% (équivalence table, non mesurée)</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.1</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Créée — poches souples F9 à charbon imprégné (combiné), mono-classe 520</t>
+          <t>Validée PA — contenu retravaillé 12/10 (données techniques fournisseur F7, 9 formats, ΔP par profondeur sans courbe, textes PA, photo Netair, codes F7CA)</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>TITABAG F9 CARB</t>
+          <t>Deltricarb GCA (fournisseur) ; v1.0 : TITABAG F9 CA</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>COMBINÉ particules+charbon (≠ charbon grains) : classe ISO 16890 F9 ePM1 80% PRIMAIRE + charbon imprégné (odeurs/COV, capacité 15%). COLMATANT → règle ePM +100 (pas const). 9,172·v²+64,135·v−10,429 ; ΔP@3400≈229. Cadre acier, 520mm, T° 40°C, feu NA. HR n.c. Photo forme poches NETBAG placeholder (média imprégné à reshooter).</t>
+          <t>v1.1 12/10/2026, décisions PA : données techniques reprises de la fiche fournisseur Deltricarb GCA (BLOC3/Fournisseurs/DELTRIAN) au lieu de TITABAG F9 CA 2021. Classe EN 779 F7 → ePM1 50 % (F7) par la table de correspondance ; média fibres de verre + grains de charbon actif ; profondeurs 635/535/380 ; formats 592/490/287×592 ; surfaces de média par référence ; ΔP fournisseur 105/130/145 Pa par profondeur (pas de courbe : clés sans_courbe + dims_dp_tableau) ; T° affichée 40 °C max. comme AZUR/NIVAL (source : 50 °C continu) ; HR 70 % ; cadre acier galvanisé et feu « Non classé » ajoutés par PA (absents de la source). Non repris : ΔP finale 450 Pa (règle gamme +100), contact alimentaire CE 1935/2004 (sans certificat). Capacité sans chiffre. Codes NETCARB-BAG-F7CA-LxHxP. Sur-mesure confirmé par PA. Photo Netair « Netcarb Bag.png ». ΔP finale : « Charbon saturé ou poches colmatées (ΔP initiale + 100 Pa) ».</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Compact charbon actif</t>
+          <t>Filtre compact miniplis, charbon actif</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -1450,22 +1450,22 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Moléculaire (ISO 10121)</t>
+          <t>Moléculaire (aucune classe ISO 10121 affichée)</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.1</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Créée — filtre moléculaire charbon actif, 2 épaisseurs 48/98 mm</t>
+          <t>Validée PA — contenu retravaillé 12/10 (sous-titre, descriptif et points clés PA, photo Netair, alignement famille, épaisseurs 48/98 corrigées, codes CA)</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>Charbon actif pur (gaz) : pas de classe ePM. ISO 10121 (LD/MD/HD à déterminer). ΔP réelles caches Excel 48/98 (cohérentes 48&gt;98), poly 7 pts. ΔP non colmatante (remplacement à saturation, capacité 15% masse). T° 40°C, HR 50%, feu NA. Nouveaux drapeaux moteur deux_epaisseurs + dp_final_mode:const. Photo CARB.png (grains) placeholder.</t>
+          <t>v1.1 12/10/2026, décisions PA : sous-titre « Filtre compact charbon actif » ; descriptif et points clés PA ; média libellé comme AZUR (sources : micro-grains) ; capacité sans chiffre (sources : 15 %) ; polluants « gaz, odeurs et COV » ; feu « Non classé » ; 40 °C max. ; HR 50 % (doc 2015) ; cadre acier galvanisé ou cellulose pelliculée ; toutes dimensions comme NETPAK S CILIA. Corrections : étiquette d'épaisseur (la courbe 98 était nommée 48 au catalogue), ligne 98 mm du tableau 73 → 67 Pa (moteur). Courbes PRISME CARB 48/98 inchangées (73/67 Pa @3400). Codes NETCARB-CILIA-CA-LxHxP. Photo « Netcarb Cilia.png ». Configurateur : efficacité figée « Charbon actif » (prix affiché d'emblée), cadre au choix -A/-C.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1673,12 +1673,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>FT-NETPAK-S-DUO</t>
+          <t>FT-NETPAK-S-CILIA-DUO</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>NETPAK S DUO</t>
+          <t>NETPAK S CILIA DUO</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1688,37 +1688,37 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Compact mini-plis + charbon actif</t>
+          <t>Compact miniplis double filtration (2 packs)</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>F7 + CA</t>
+          <t>M5 → F9</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>ePM1 50% + CA</t>
+          <t>ePM10 50% → ePM1 80% (+ charbon actif)</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.1</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Créée — mono-classe F7 GREENTEX + charbon actif (ep48)</t>
+          <t>Validée PA — contenu retravaillé 12/10 (renommé NETPAK S CILIA DUO, 2 packs miniplis, plage M5 → F9, courbe ePM1 50 % (F7) + charbon, textes et photo PA)</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>Fiches_Netair/Fiche technique NETPAK S DUO.html</t>
+          <t>Fiches_Netair/Fiche technique NETPAK S CILIA DUO.html</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>F7 GREENTEX + charbon actif. ΔP combinée 36→247 Pa (nom 190). Feu NA (charbon non classé). Surface média dév. ≈12,55 m². ΔP finale +100 Pa (= règle Titanair PDC init+100). Photo placeholder PRISME A à remplacer. Capacité CA (grammage) non communiquée → R&amp;D. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t>
+          <t>v1.1 12/10/2026, décisions PA : renommé NETPAK S CILIA DUO partout (ex-NETPAK S DUO, slug netpak-s-cilia-duo) ; DUO = 2 packs miniplis dans un cadre, particules + particules (ex. M5F7) ou particules + charbon (F7CA) ; plage M5 → F9 annoncée (modèle BORA) ; courbe et calculateur ePM1 50 % (F7) + charbon 48 mm (source DUO F7 GR-CA ep48 du 10/10/2022 : 36…247 Pa, 190 Pa @3400) ; 60 °C (65 °C / 1 h) ; feu M1 (particulaire) / non classé (charbon) ; cadre acier galvanisé ou cellulose pelliculée (CODIFICATION_PRODUITS.md mise à jour) ; capacité sans chiffre. Retirés car non sourcés : surface 12,6 m², HR 100 %. Codes NETPAK-CILIA-DUO-F7CA-LxHxP (clé ref_base). Configurateur : sur devis, Efficacité 1 et 2 (M5 → F9 + charbon, sans doublon, CA en fin de code), cadre au choix. Titre 26 px pour tenir sur une ligne. Photo Netair en écorché.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Filtre polydièdre T.H.E</t>
+          <t>Filtre absolu caisson multidièdre</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>v1.1</t>
+          <t>v1.2</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>Contenu retravaillé v1.1 — courbes E10 + H13 réelles, 4 formats, cadre 610×610 corrigé (H14 à mesurer)</t>
+          <t>Validée PA — contenu retravaillé v1.1 (15/08) ; v1.2 (12/10) : « caisson multidièdre » (sous-titre, descriptif, Type), badge « Filtre absolu (T.H.E) »</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>Validée PA — contenu retravaillé (photo à remplacer)</t>
+          <t>Validée PA — contenu retravaillé (photo Netair depuis le 22/09)</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Contenu retravaillé v1.1 (02/08) — v1.2 (15/08) : ligne « Séparateur : Hot melt » ajoutée (accord PA)</t>
+          <t>Validée PA (12/10/2026, sans retouche) — contenu retravaillé v1.1 (02/08), v1.2 (15/08)</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -959,17 +959,17 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>v1.1</t>
+          <t>v1.2</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Validée PA — contenu retravaillé 26/07 (densité progressive, stock F7 par défaut, courbe/curseur bornés 4 000, boutique code 17 : standard 380/550 chiffrés, G4/M5 et sur-mesure en devis)</t>
+          <t>Validée PA — contenu retravaillé 26/07 (densité progressive, stock F7 par défaut, courbe/curseur bornés 4 000, boutique code 17 : standard 380/550 chiffrés, G4/M5 et sur-mesure en devis) ; v1.2 12/10 : mise en page corrigée, la fiche sortait sur 4 pages à l'impression (accord PA)</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -959,7 +959,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>v1.2</t>
+          <t>v1.3</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Validée PA — contenu retravaillé 26/07 (densité progressive, stock F7 par défaut, courbe/curseur bornés 4 000, boutique code 17 : standard 380/550 chiffrés, G4/M5 et sur-mesure en devis) ; v1.2 12/10 : mise en page corrigée, la fiche sortait sur 4 pages à l'impression (accord PA)</t>
+          <t>Validée PA — contenu retravaillé 26/07 (densité progressive, stock F7 par défaut, courbe/curseur bornés 4 000, boutique code 17 : standard 380/550 chiffrés, G4/M5 et sur-mesure en devis) ; v1.2 12/10 : mise en page corrigée, la fiche sortait sur 4 pages à l'impression (accord PA) ; v1.3 12/10 : courbe et ligne M5 550 mm retirées (mesure incohérente, à mesurer), plus aucune mention « à valider » (accord PA)</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1145,17 +1145,17 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>v1.2</t>
+          <t>v1.3</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Validée PA — contenu retravaillé 17/07 ; v1.2 18/07 : ABS retiré, parois « Plastique » (gamme M5 → F9 ; photo à remplacer)</t>
+          <t>Validée PA — contenu retravaillé 17/07 ; v1.2 18/07 : ABS retiré, parois « Plastique » (gamme M5 → F9 ; photo à remplacer) ; v1.3 (12/10) : F7 = ePM1 50 % (média GREENTEX, comme CILIA et BORA), décision PA du 12/10 confirmant celle du 03/07</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
@@ -1269,17 +1269,17 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>v1.2</t>
+          <t>v1.3</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Validée PA (12/10/2026, sans retouche) — contenu retravaillé v1.1 (02/08), v1.2 (15/08)</t>
+          <t>Validée PA (12/10/2026, sans retouche) — contenu retravaillé v1.1 (02/08), v1.2 (15/08) ; v1.3 (12/10) : calculateur corrigé, « ΔP finale = 2 × ΔP initiale, EN 1822 » (régression du 22/09 relevée par l'audit, accord PA)</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>v1.2</t>
+          <t>v1.3</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>Validée PA — contenu retravaillé v1.1 (15/08) ; v1.2 (12/10) : « caisson multidièdre » (sous-titre, descriptif, Type), badge « Filtre absolu (T.H.E) »</t>
+          <t>Validée PA — contenu retravaillé v1.1 (15/08) ; v1.2 (12/10) : « caisson multidièdre » (sous-titre, descriptif, Type), badge « Filtre absolu (T.H.E) » ; v1.3 (12/10) : calculateur corrigé, « ΔP finale = 2 × ΔP initiale, EN 1822 » (régression du 22/09 relevée par l'audit, accord PA)</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -897,17 +897,17 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>v1.2</t>
+          <t>v1.3</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Validée PA — contenu retravaillé 16/07</t>
+          <t>Validée PA — contenu retravaillé 16/07 ; v1.3 (12/10) : badges alignés sur la gamme réelle « Coarse 40 % → 65 % (G2 → G4) » au lieu de « Coarse 65 % (G4) » (audit, accord PA)</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
